--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -31824,7 +31824,7 @@
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
-        <v>45940.6493981481</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1170" t="n">
         <v>86500</v>
@@ -31845,6 +31845,32 @@
         <v>35</v>
       </c>
       <c r="H1170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>45943.649375</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>58325</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1171" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1171" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -31850,7 +31850,7 @@
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
-        <v>45943.649375</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1171" t="n">
         <v>58325</v>
@@ -31871,6 +31871,32 @@
         <v>35</v>
       </c>
       <c r="H1171" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>45944.6493402778</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>30934</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1172" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1172" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1092,6 +1092,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.11500000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29500007629395</t>
   </si>
 </sst>
 </file>
@@ -31876,7 +31879,7 @@
     </row>
     <row r="1172">
       <c r="A1172" s="1" t="n">
-        <v>45944.6493402778</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1172" t="n">
         <v>30934</v>
@@ -31897,6 +31900,32 @@
         <v>35</v>
       </c>
       <c r="H1172" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>45945.6496064815</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>37248</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="G1173" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1173" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -31905,7 +31905,7 @@
     </row>
     <row r="1173">
       <c r="A1173" s="1" t="n">
-        <v>45945.6496064815</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1173" t="n">
         <v>37248</v>
@@ -31926,6 +31926,32 @@
         <v>360</v>
       </c>
       <c r="H1173" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>45946.6493287037</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>27672</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1174" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1174" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -31931,7 +31931,7 @@
     </row>
     <row r="1174">
       <c r="A1174" s="1" t="n">
-        <v>45946.6493287037</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1174" t="n">
         <v>27672</v>
@@ -31952,6 +31952,32 @@
         <v>35</v>
       </c>
       <c r="H1174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
+        <v>45947.6448726852</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>22193</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1175" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1175" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -31957,7 +31957,7 @@
     </row>
     <row r="1175">
       <c r="A1175" s="1" t="n">
-        <v>45947.6448726852</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1175" t="n">
         <v>22193</v>
@@ -31978,6 +31978,32 @@
         <v>35</v>
       </c>
       <c r="H1175" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>45950.6493518519</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>36537</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1176" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1176" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -31983,7 +31983,7 @@
     </row>
     <row r="1176">
       <c r="A1176" s="1" t="n">
-        <v>45950.6493518519</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1176" t="n">
         <v>36537</v>
@@ -32004,6 +32004,32 @@
         <v>35</v>
       </c>
       <c r="H1176" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="1" t="n">
+        <v>45951.6494791667</v>
+      </c>
+      <c r="B1177" t="n">
+        <v>74379</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1177" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1177" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32009,7 +32009,7 @@
     </row>
     <row r="1177">
       <c r="A1177" s="1" t="n">
-        <v>45951.6494791667</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1177" t="n">
         <v>74379</v>
@@ -32030,6 +32030,32 @@
         <v>35</v>
       </c>
       <c r="H1177" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="n">
+        <v>45952.6061226852</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>24038</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1178" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1178" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32035,7 +32035,7 @@
     </row>
     <row r="1178">
       <c r="A1178" s="1" t="n">
-        <v>45952.6061226852</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1178" t="n">
         <v>24038</v>
@@ -32056,6 +32056,32 @@
         <v>35</v>
       </c>
       <c r="H1178" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="n">
+        <v>45953.5637615741</v>
+      </c>
+      <c r="B1179" t="n">
+        <v>15350</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1179" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1179" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32061,7 +32061,7 @@
     </row>
     <row r="1179">
       <c r="A1179" s="1" t="n">
-        <v>45953.5637615741</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1179" t="n">
         <v>15350</v>
@@ -32082,6 +32082,32 @@
         <v>35</v>
       </c>
       <c r="H1179" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>45954.635787037</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>38058</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1180" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1180" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32087,7 +32087,7 @@
     </row>
     <row r="1180">
       <c r="A1180" s="1" t="n">
-        <v>45954.635787037</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1180" t="n">
         <v>38058</v>
@@ -32108,6 +32108,32 @@
         <v>35</v>
       </c>
       <c r="H1180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>45957.6759837963</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>16457</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1181" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1181" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32113,7 +32113,7 @@
     </row>
     <row r="1181">
       <c r="A1181" s="1" t="n">
-        <v>45957.6759837963</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1181" t="n">
         <v>16457</v>
@@ -32134,6 +32134,32 @@
         <v>35</v>
       </c>
       <c r="H1181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>45958.662974537</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>12946</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1182" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1182" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32139,7 +32139,7 @@
     </row>
     <row r="1182">
       <c r="A1182" s="1" t="n">
-        <v>45958.662974537</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1182" t="n">
         <v>12946</v>
@@ -32160,6 +32160,32 @@
         <v>35</v>
       </c>
       <c r="H1182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="n">
+        <v>45959.6468634259</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>20217</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1183" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1183" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32165,7 +32165,7 @@
     </row>
     <row r="1183">
       <c r="A1183" s="1" t="n">
-        <v>45959.6468634259</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1183" t="n">
         <v>20217</v>
@@ -32186,6 +32186,32 @@
         <v>35</v>
       </c>
       <c r="H1183" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>45960.6666898148</v>
+      </c>
+      <c r="B1184" t="n">
+        <v>29501</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1184" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1184" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32191,7 +32191,7 @@
     </row>
     <row r="1184">
       <c r="A1184" s="1" t="n">
-        <v>45960.6666898148</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1184" t="n">
         <v>29501</v>
@@ -32212,6 +32212,32 @@
         <v>35</v>
       </c>
       <c r="H1184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="n">
+        <v>45961.6680555556</v>
+      </c>
+      <c r="B1185" t="n">
+        <v>7190</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1185" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1185" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32217,7 +32217,7 @@
     </row>
     <row r="1185">
       <c r="A1185" s="1" t="n">
-        <v>45961.6680555556</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1185" t="n">
         <v>7190</v>
@@ -32238,6 +32238,32 @@
         <v>35</v>
       </c>
       <c r="H1185" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="n">
+        <v>45964.6286689815</v>
+      </c>
+      <c r="B1186" t="n">
+        <v>59850</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1186" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1186" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32243,7 +32243,7 @@
     </row>
     <row r="1186">
       <c r="A1186" s="1" t="n">
-        <v>45964.6286689815</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1186" t="n">
         <v>59850</v>
@@ -32264,6 +32264,32 @@
         <v>35</v>
       </c>
       <c r="H1186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>45965.6820833333</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>12900</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1187" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1187" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32269,7 +32269,7 @@
     </row>
     <row r="1187">
       <c r="A1187" s="1" t="n">
-        <v>45965.6820833333</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1187" t="n">
         <v>12900</v>
@@ -32290,6 +32290,32 @@
         <v>35</v>
       </c>
       <c r="H1187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>45966.6491666667</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>9470</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1188" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1188" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32295,13 +32295,13 @@
     </row>
     <row r="1188">
       <c r="A1188" s="1" t="n">
-        <v>45966.6491666667</v>
+        <v>45967.6669560185</v>
       </c>
       <c r="B1188" t="n">
-        <v>9470</v>
+        <v>9901</v>
       </c>
       <c r="C1188" t="n">
-        <v>4.28999996185303</v>
+        <v>4.29500007629395</v>
       </c>
       <c r="D1188" t="n">
         <v>4.28999996185303</v>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32295,10 +32295,10 @@
     </row>
     <row r="1188">
       <c r="A1188" s="1" t="n">
-        <v>45967.6669560185</v>
+        <v>45968.6851041667</v>
       </c>
       <c r="B1188" t="n">
-        <v>9901</v>
+        <v>14186</v>
       </c>
       <c r="C1188" t="n">
         <v>4.29500007629395</v>
@@ -32307,7 +32307,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="E1188" t="n">
-        <v>4.28999996185303</v>
+        <v>4.29500007629395</v>
       </c>
       <c r="F1188" t="n">
         <v>4.28999996185303</v>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32295,19 +32295,19 @@
     </row>
     <row r="1188">
       <c r="A1188" s="1" t="n">
-        <v>45968.6851041667</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1188" t="n">
-        <v>14186</v>
+        <v>9470</v>
       </c>
       <c r="C1188" t="n">
-        <v>4.29500007629395</v>
+        <v>4.28999996185303</v>
       </c>
       <c r="D1188" t="n">
         <v>4.28999996185303</v>
       </c>
       <c r="E1188" t="n">
-        <v>4.29500007629395</v>
+        <v>4.28999996185303</v>
       </c>
       <c r="F1188" t="n">
         <v>4.28999996185303</v>
@@ -32316,6 +32316,84 @@
         <v>35</v>
       </c>
       <c r="H1188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1189" t="n">
+        <v>9901</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1189" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>14186</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1190" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>45971.5795023148</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>4125</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="G1191" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1191" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1095,6 +1095,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.29500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25500011444092</t>
   </si>
 </sst>
 </file>
@@ -32373,7 +32376,7 @@
     </row>
     <row r="1191">
       <c r="A1191" s="1" t="n">
-        <v>45971.5795023148</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B1191" t="n">
         <v>4125</v>
@@ -32394,6 +32397,32 @@
         <v>175</v>
       </c>
       <c r="H1191" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>45972.6780439815</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>17665</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>4.24499988555908</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>4.25500011444092</v>
+      </c>
+      <c r="G1192" t="s">
+        <v>361</v>
+      </c>
+      <c r="H1192" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32402,7 +32402,7 @@
     </row>
     <row r="1192">
       <c r="A1192" s="1" t="n">
-        <v>45972.6780439815</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1192" t="n">
         <v>17665</v>
@@ -32423,6 +32423,32 @@
         <v>361</v>
       </c>
       <c r="H1192" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>45973.69125</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>41116</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="G1193" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1193" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32428,7 +32428,7 @@
     </row>
     <row r="1193">
       <c r="A1193" s="1" t="n">
-        <v>45973.69125</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B1193" t="n">
         <v>41116</v>
@@ -32449,6 +32449,32 @@
         <v>38</v>
       </c>
       <c r="H1193" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>45974.6271759259</v>
+      </c>
+      <c r="B1194" t="n">
+        <v>19771</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="G1194" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1194" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32454,7 +32454,7 @@
     </row>
     <row r="1194">
       <c r="A1194" s="1" t="n">
-        <v>45974.6271759259</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B1194" t="n">
         <v>19771</v>
@@ -32475,6 +32475,32 @@
         <v>143</v>
       </c>
       <c r="H1194" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>45975.6325578704</v>
+      </c>
+      <c r="B1195" t="n">
+        <v>13975</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="G1195" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1195" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32480,7 +32480,7 @@
     </row>
     <row r="1195">
       <c r="A1195" s="1" t="n">
-        <v>45975.6325578704</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1195" t="n">
         <v>13975</v>
@@ -32501,6 +32501,32 @@
         <v>143</v>
       </c>
       <c r="H1195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>45978.6852314815</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>59946</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="G1196" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1196" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32506,7 +32506,7 @@
     </row>
     <row r="1196">
       <c r="A1196" s="1" t="n">
-        <v>45978.6852314815</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B1196" t="n">
         <v>59946</v>
@@ -32527,6 +32527,32 @@
         <v>360</v>
       </c>
       <c r="H1196" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>45979.6795023148</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>33644</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1197" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1197" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32532,7 +32532,7 @@
     </row>
     <row r="1197">
       <c r="A1197" s="1" t="n">
-        <v>45979.6795023148</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B1197" t="n">
         <v>33644</v>
@@ -32553,6 +32553,32 @@
         <v>35</v>
       </c>
       <c r="H1197" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>45980.6844560185</v>
+      </c>
+      <c r="B1198" t="n">
+        <v>60896</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1198" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1198" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32558,7 +32558,7 @@
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="n">
-        <v>45980.6844560185</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1198" t="n">
         <v>60896</v>
@@ -32579,6 +32579,32 @@
         <v>35</v>
       </c>
       <c r="H1198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>45981.6774652778</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>3686</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1199" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32584,7 +32584,7 @@
     </row>
     <row r="1199">
       <c r="A1199" s="1" t="n">
-        <v>45981.6774652778</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1199" t="n">
         <v>3686</v>
@@ -32605,6 +32605,32 @@
         <v>35</v>
       </c>
       <c r="H1199" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>45982.69125</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>22500</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1200" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1200" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32610,7 +32610,7 @@
     </row>
     <row r="1200">
       <c r="A1200" s="1" t="n">
-        <v>45982.69125</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1200" t="n">
         <v>22500</v>
@@ -32631,6 +32631,32 @@
         <v>35</v>
       </c>
       <c r="H1200" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>45985.6911111111</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>41637</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1201" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32636,7 +32636,7 @@
     </row>
     <row r="1201">
       <c r="A1201" s="1" t="n">
-        <v>45985.6911111111</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1201" t="n">
         <v>41637</v>
@@ -32657,6 +32657,32 @@
         <v>360</v>
       </c>
       <c r="H1201" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>45986.6714930556</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>57448</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1202" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32662,7 +32662,7 @@
     </row>
     <row r="1202">
       <c r="A1202" s="1" t="n">
-        <v>45986.6714930556</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1202" t="n">
         <v>57448</v>
@@ -32683,6 +32683,32 @@
         <v>33</v>
       </c>
       <c r="H1202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>45987.6804282407</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>38060</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1203" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1098,6 +1098,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.25500011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499982833862</t>
   </si>
 </sst>
 </file>
@@ -32688,7 +32691,7 @@
     </row>
     <row r="1203">
       <c r="A1203" s="1" t="n">
-        <v>45987.6804282407</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1203" t="n">
         <v>38060</v>
@@ -32709,6 +32712,32 @@
         <v>33</v>
       </c>
       <c r="H1203" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>45988.6911342593</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>145197</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>362</v>
+      </c>
+      <c r="H1204" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32717,7 +32717,7 @@
     </row>
     <row r="1204">
       <c r="A1204" s="1" t="n">
-        <v>45988.6911342593</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1204" t="n">
         <v>145197</v>
@@ -32738,6 +32738,32 @@
         <v>362</v>
       </c>
       <c r="H1204" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>45989.6755902778</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>26588</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1205" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32743,7 +32743,7 @@
     </row>
     <row r="1205">
       <c r="A1205" s="1" t="n">
-        <v>45989.6755902778</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B1205" t="n">
         <v>26588</v>
@@ -32764,6 +32764,32 @@
         <v>33</v>
       </c>
       <c r="H1205" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>45992.6910763889</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>135903</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G1206" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1206" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32769,7 +32769,7 @@
     </row>
     <row r="1206">
       <c r="A1206" s="1" t="n">
-        <v>45992.6910763889</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B1206" t="n">
         <v>135903</v>
@@ -32790,6 +32790,32 @@
         <v>33</v>
       </c>
       <c r="H1206" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>45993.6911226852</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>104261</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>4.30999994277954</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>4.30999994277954</v>
+      </c>
+      <c r="G1207" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1207" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32795,7 +32795,7 @@
     </row>
     <row r="1207">
       <c r="A1207" s="1" t="n">
-        <v>45993.6911226852</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B1207" t="n">
         <v>104261</v>
@@ -32816,6 +32816,32 @@
         <v>140</v>
       </c>
       <c r="H1207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>45994.6912615741</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>36195</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="G1208" t="s">
+        <v>362</v>
+      </c>
+      <c r="H1208" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32821,7 +32821,7 @@
     </row>
     <row r="1208">
       <c r="A1208" s="1" t="n">
-        <v>45994.6912615741</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1208" t="n">
         <v>36195</v>
@@ -32842,6 +32842,32 @@
         <v>362</v>
       </c>
       <c r="H1208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>45995.6912962963</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>14595</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>4.2649998664856</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1209" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1209" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32847,13 +32847,13 @@
     </row>
     <row r="1209">
       <c r="A1209" s="1" t="n">
-        <v>45995.6912962963</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B1209" t="n">
         <v>14595</v>
       </c>
       <c r="C1209" t="n">
-        <v>4.28499984741211</v>
+        <v>4.28999996185303</v>
       </c>
       <c r="D1209" t="n">
         <v>4.2649998664856</v>
@@ -32868,6 +32868,32 @@
         <v>35</v>
       </c>
       <c r="H1209" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>45996.6725462963</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>20747</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="G1210" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1210" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1101,6 +1101,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.30499982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28499984741211</t>
   </si>
 </sst>
 </file>
@@ -32873,7 +32876,7 @@
     </row>
     <row r="1210">
       <c r="A1210" s="1" t="n">
-        <v>45996.6725462963</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B1210" t="n">
         <v>20747</v>
@@ -32894,6 +32897,32 @@
         <v>143</v>
       </c>
       <c r="H1210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="n">
+        <v>45999.6909722222</v>
+      </c>
+      <c r="B1211" t="n">
+        <v>4380</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="G1211" t="s">
+        <v>363</v>
+      </c>
+      <c r="H1211" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32902,7 +32902,7 @@
     </row>
     <row r="1211">
       <c r="A1211" s="1" t="n">
-        <v>45999.6909722222</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B1211" t="n">
         <v>4380</v>
@@ -32923,6 +32923,32 @@
         <v>363</v>
       </c>
       <c r="H1211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>46000.6808333333</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>5373</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="G1212" t="s">
+        <v>363</v>
+      </c>
+      <c r="H1212" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32928,7 +32928,7 @@
     </row>
     <row r="1212">
       <c r="A1212" s="1" t="n">
-        <v>46000.6808333333</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B1212" t="n">
         <v>5373</v>
@@ -32949,6 +32949,32 @@
         <v>363</v>
       </c>
       <c r="H1212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46001.522650463</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>4.28499984741211</v>
+      </c>
+      <c r="G1213" t="s">
+        <v>363</v>
+      </c>
+      <c r="H1213" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32954,7 +32954,7 @@
     </row>
     <row r="1213">
       <c r="A1213" s="1" t="n">
-        <v>46001.522650463</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B1213" t="n">
         <v>3200</v>
@@ -32975,6 +32975,32 @@
         <v>363</v>
       </c>
       <c r="H1213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46002.6834490741</v>
+      </c>
+      <c r="B1214" t="n">
+        <v>22887</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1214" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1214" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -32980,7 +32980,7 @@
     </row>
     <row r="1214">
       <c r="A1214" s="1" t="n">
-        <v>46002.6834490741</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B1214" t="n">
         <v>22887</v>
@@ -33001,6 +33001,32 @@
         <v>35</v>
       </c>
       <c r="H1214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46003.6872222222</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>25370</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1215" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -33006,7 +33006,7 @@
     </row>
     <row r="1215">
       <c r="A1215" s="1" t="n">
-        <v>46003.6872222222</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B1215" t="n">
         <v>25370</v>
@@ -33027,6 +33027,32 @@
         <v>360</v>
       </c>
       <c r="H1215" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>46006.6912615741</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>25318</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1216" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1216" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -33032,7 +33032,7 @@
     </row>
     <row r="1216">
       <c r="A1216" s="1" t="n">
-        <v>46006.6912615741</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B1216" t="n">
         <v>25318</v>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -33056,6 +33056,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46007.3333333333</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1217" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1217" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIW.MI.xlsx
+++ b/data/AIW.MI.xlsx
@@ -33082,6 +33082,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46008.3333333333</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1218" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
